--- a/target/test-classes/output/pro/ProExecutionData.xlsx
+++ b/target/test-classes/output/pro/ProExecutionData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t xml:space="preserve">TestCase</t>
   </si>
@@ -62,6 +62,30 @@
   </si>
   <si>
     <t xml:space="preserve">Pro E2E With Mandatory Fields</t>
+  </si>
+  <si>
+    <t>Automation Portfolio_20260831_130940_442</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Automation Product_20260831_130945_642</t>
+  </si>
+  <si>
+    <t>Automation Product_20260831_130945_642: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20260831_130945_642: Automation Feature_20260831_131011_597</t>
+  </si>
+  <si>
+    <t>Automation Feature_20260831_131011_597: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Collaborative Tools</t>
+  </si>
+  <si>
+    <t>Figma</t>
   </si>
 </sst>
 </file>
@@ -354,11 +378,11 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.57"/>
+    <col min="1" max="1" customWidth="true" hidden="false" style="0" width="27.15" collapsed="false" outlineLevel="0"/>
+    <col min="2" max="2" customWidth="true" hidden="false" style="0" width="13.57" collapsed="false" outlineLevel="0"/>
+    <col min="3" max="3" customWidth="true" hidden="false" style="0" width="13.0" collapsed="false" outlineLevel="0"/>
+    <col min="4" max="4" customWidth="true" hidden="false" style="0" width="12.85" collapsed="false" outlineLevel="0"/>
+    <col min="5" max="5" customWidth="true" hidden="false" style="0" width="19.57" collapsed="false" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -406,16 +430,42 @@
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="B2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C2" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
